--- a/22_image_to_excel/test_evidence.xlsx
+++ b/22_image_to_excel/test_evidence.xlsx
@@ -9,7 +9,7 @@
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="No.1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="No.2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="No.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="No.21" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
